--- a/laporan_padel_dki_jakarta_2026-10-07.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-07.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.685.000</t>
+          <t>Rp2.985.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp33.400.000</t>
+          <t>Rp34.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp4.750.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.949.994</t>
+          <t>Rp2.699.994</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.729.000</t>
+          <t>Rp5.844.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-07.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-07.xlsx
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.325.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp915.000</t>
+          <t>Rp615.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.074.000</t>
+          <t>Rp2.214.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>85</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.769.000</t>
+          <t>Rp3.542.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.870.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>96</v>
       </c>
       <c r="D48" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.437.000</t>
+          <t>Rp3.536.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.168.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.394.000</t>
+          <t>Rp1.194.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.360.000</t>
+          <t>Rp1.435.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp4.655.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.875.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp5.625.000</t>
+          <t>Rp5.825.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.140.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp972.000</t>
+          <t>Rp1.134.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.185.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.423.000</t>
+          <t>Rp3.621.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.410.000</t>
+          <t>Rp4.225.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp3.440.000</t>
+          <t>Rp3.640.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>54</v>
       </c>
       <c r="D44" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp106.000</t>
+          <t>Rp212.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>64</v>
       </c>
       <c r="D62" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp9.000.000</t>
+          <t>Rp9.600.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>34</v>
       </c>
       <c r="D63" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp390.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>144</v>
       </c>
       <c r="D67" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp9.100.000</t>
+          <t>Rp9.300.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>30</v>
       </c>
       <c r="D69" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp3.080.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.875.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp34.200.000</t>
+          <t>Rp35.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.750.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.525.000</t>
+          <t>Rp5.175.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.887.000</t>
+          <t>Rp7.137.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.700.000</t>
+          <t>Rp21.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>48</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp399.000</t>
+          <t>Rp559.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp675.000</t>
+          <t>Rp585.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp1.925.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp11.575.000</t>
+          <t>Rp11.965.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp7.875.000</t>
+          <t>Rp8.125.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp26.500.000</t>
+          <t>Rp29.000.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp4.750.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.040.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.175.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.699.994</t>
+          <t>Rp2.824.994</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp630.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.490.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp904.000</t>
+          <t>Rp1.302.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.860.000</t>
+          <t>Rp4.325.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.725.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp963.000</t>
+          <t>Rp794.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-07.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-07.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.985.000</t>
+          <t>Rp3.183.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.275.000</t>
+          <t>Rp5.525.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.830.000</t>
+          <t>Rp6.605.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.787.500</t>
+          <t>Rp9.265.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.875.000</t>
+          <t>Rp6.825.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.632.000</t>
+          <t>Rp1.952.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>136</v>
       </c>
       <c r="D22" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp10.725.000</t>
+          <t>Rp11.000.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.350.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp615.000</t>
+          <t>Rp740.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.214.000</t>
+          <t>Rp2.412.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.158.000</t>
+          <t>Rp2.306.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.508.000</t>
+          <t>Rp2.607.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp2.875.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.168.000</t>
+          <t>Rp3.456.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>28</v>
       </c>
       <c r="D53" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp891.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>36</v>
       </c>
       <c r="D55" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp3.350.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>80</v>
       </c>
       <c r="D61" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.194.000</t>
+          <t>Rp1.294.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp8.160.000</t>
+          <t>Rp8.460.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>34</v>
       </c>
       <c r="D69" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.282.000</t>
+          <t>Rp4.780.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.435.000</t>
+          <t>Rp1.095.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>114</v>
       </c>
       <c r="D80" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>54</v>
       </c>
       <c r="D82" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp2.783.000</t>
+          <t>Rp2.981.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>36</v>
       </c>
       <c r="D87" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp5.520.000</t>
+          <t>Rp7.040.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.140.000</t>
+          <t>Rp3.390.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp4.195.000</t>
+          <t>Rp3.775.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.556.000</t>
+          <t>Rp4.512.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.300.000</t>
+          <t>Rp8.900.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp125.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp14.750.000</t>
+          <t>Rp15.450.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp5.475.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>34</v>
       </c>
       <c r="D22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.830.000</t>
+          <t>Rp1.245.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp4.160.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp15.450.000</t>
+          <t>Rp16.200.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>54</v>
       </c>
       <c r="D44" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.460.000</t>
+          <t>Rp10.212.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp7.800.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp212.000</t>
+          <t>Rp265.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D58" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp880.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>144</v>
       </c>
       <c r="D67" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp9.300.000</t>
+          <t>Rp9.800.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.875.000</t>
+          <t>Rp5.225.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.050.000</t>
+          <t>Rp6.770.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.158.000</t>
+          <t>Rp3.457.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.175.000</t>
+          <t>Rp5.525.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.760.000</t>
+          <t>Rp3.060.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp2.994.000</t>
+          <t>Rp4.992.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp436.000</t>
+          <t>Rp605.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp11.325.000</t>
+          <t>Rp13.100.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.137.000</t>
+          <t>Rp7.387.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.385.000</t>
+          <t>Rp6.059.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.225.000</t>
+          <t>Rp7.375.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.610.000</t>
+          <t>Rp7.772.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp4.100.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp11.965.000</t>
+          <t>Rp12.455.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp8.125.000</t>
+          <t>Rp8.925.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>84</v>
       </c>
       <c r="D35" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.822.000</t>
+          <t>Rp3.120.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.700.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp18.310.000</t>
+          <t>Rp18.910.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>98</v>
       </c>
       <c r="D48" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp8.820.000</t>
+          <t>Rp8.970.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.450.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.840.000</t>
+          <t>Rp7.740.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.392.000</t>
+          <t>Rp1.196.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.190.000</t>
+          <t>Rp1.040.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.335.000</t>
+          <t>Rp7.635.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.160.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.685.000</t>
+          <t>Rp9.235.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.425.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp2.075.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.525.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp26.210.000</t>
+          <t>Rp26.810.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp2.430.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.270.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.302.000</t>
+          <t>Rp1.700.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.325.000</t>
+          <t>Rp4.790.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.570.000</t>
+          <t>Rp3.165.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>51</v>
       </c>
       <c r="D38" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp185.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp3.875.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>68</v>
       </c>
       <c r="D43" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp240.000</t>
+          <t>Rp360.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-07.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-07.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.183.000</t>
+          <t>Rp3.483.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.608.000</t>
+          <t>Rp1.878.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp6.605.000</t>
+          <t>Rp7.105.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp9.265.500</t>
+          <t>Rp10.915.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.952.000</t>
+          <t>Rp2.528.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.195.000</t>
+          <t>Rp4.470.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp15.375.000</t>
+          <t>Rp15.680.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.355.000</t>
+          <t>Rp4.975.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.498.000</t>
+          <t>Rp4.598.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.607.000</t>
+          <t>Rp3.027.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>42</v>
       </c>
       <c r="D46" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.750.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>96</v>
       </c>
       <c r="D48" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.536.000</t>
+          <t>Rp3.833.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>105</v>
       </c>
       <c r="D49" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.075.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp498.000</t>
+          <t>Rp698.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp4.832.000</t>
+          <t>Rp5.600.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>32</v>
       </c>
       <c r="D68" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp780.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>176</v>
       </c>
       <c r="D70" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.780.000</t>
+          <t>Rp5.876.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>68</v>
       </c>
       <c r="D72" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp360.000</t>
+          <t>Rp720.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>96</v>
       </c>
       <c r="D75" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp3.660.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp1.770.000</t>
+          <t>Rp2.580.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>45</v>
       </c>
       <c r="D77" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>80</v>
       </c>
       <c r="D88" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp1.791.000</t>
+          <t>Rp3.285.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp5.825.000</t>
+          <t>Rp4.250.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>90</v>
       </c>
       <c r="D90" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp3.840.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp415.000</t>
+          <t>Rp465.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rp60.000 - Rp150.000</t>
+          <t>Rp60.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.390.000</t>
+          <t>Rp3.710.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>68</v>
       </c>
       <c r="D98" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp3.775.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.188.500</t>
+          <t>Rp15.328.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.512.000</t>
+          <t>Rp6.068.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.900.000</t>
+          <t>Rp8.550.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.621.000</t>
+          <t>Rp3.796.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.225.000</t>
+          <t>Rp6.200.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp175.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.680.000</t>
+          <t>Rp3.960.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp15.450.000</t>
+          <t>Rp17.050.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.475.000</t>
+          <t>Rp6.375.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.190.000</t>
+          <t>Rp6.735.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>63</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.255.000</t>
+          <t>Rp2.795.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.575.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp16.200.000</t>
+          <t>Rp16.650.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>54</v>
       </c>
       <c r="D44" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp3.325.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp265.000</t>
+          <t>Rp318.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D58" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp1.240.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>84</v>
       </c>
       <c r="D66" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp9.700.000</t>
+          <t>Rp10.050.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>90</v>
       </c>
       <c r="D71" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp22.467.500</t>
+          <t>Rp22.275.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp7.150.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.810.000</t>
+          <t>Rp2.270.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.770.000</t>
+          <t>Rp6.470.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.457.000</t>
+          <t>Rp3.782.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.375.000</t>
+          <t>Rp9.045.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.525.000</t>
+          <t>Rp5.875.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.060.000</t>
+          <t>Rp3.345.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.190.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6319,16 +6319,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp456.000</t>
+          <t>Rp684.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6350,16 +6350,16 @@
         <v>64</v>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.992.000</t>
+          <t>Rp5.491.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.830.000</t>
+          <t>Rp10.530.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp8.300.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp605.000</t>
+          <t>Rp804.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.100.000</t>
+          <t>Rp13.690.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp7.387.000</t>
+          <t>Rp7.859.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp14.365.000</t>
+          <t>Rp14.595.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp7.375.000</t>
+          <t>Rp6.975.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>42</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp6.194.000</t>
+          <t>Rp5.118.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp594.000</t>
+          <t>Rp693.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp10.125.000</t>
+          <t>Rp8.375.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.772.000</t>
+          <t>Rp8.570.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>60</v>
       </c>
       <c r="D29" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.070.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.485.000</t>
+          <t>Rp3.055.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp8.925.000</t>
+          <t>Rp12.150.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>84</v>
       </c>
       <c r="D35" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.120.000</t>
+          <t>Rp3.690.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp4.075.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>34</v>
       </c>
       <c r="D37" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp576.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp18.910.000</t>
+          <t>Rp19.960.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp7.699.000</t>
+          <t>Rp8.499.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp29.000.000</t>
+          <t>Rp29.200.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.720.000</t>
+          <t>Rp2.620.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp5.450.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp7.740.000</t>
+          <t>Rp9.120.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.196.000</t>
+          <t>Rp897.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.635.000</t>
+          <t>Rp7.125.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.160.000</t>
+          <t>Rp4.490.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.824.994</t>
+          <t>Rp3.399.993</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp792.000</t>
+          <t>Rp891.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.844.000</t>
+          <t>Rp5.739.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp26.810.000</t>
+          <t>Rp28.070.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp160.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.270.000</t>
+          <t>Rp4.635.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.700.000</t>
+          <t>Rp2.297.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.790.000</t>
+          <t>Rp5.075.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp7.800.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp2.650.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp295.000</t>
+          <t>Rp1.180.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D35" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.695.000</t>
+          <t>Rp2.445.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D36" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp930.000</t>
+          <t>Rp1.520.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>51</v>
       </c>
       <c r="D38" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp185.000</t>
+          <t>Rp555.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp3.875.000</t>
+          <t>Rp4.275.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>64</v>
       </c>
       <c r="D41" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp794.000</t>
+          <t>Rp963.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-07.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-07.xlsx
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.550.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.964.985</t>
+          <t>Rp6.615.986</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.915.500</t>
+          <t>Rp11.740.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.360.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.306.000</t>
+          <t>Rp2.158.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.920.000</t>
+          <t>Rp3.220.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>36</v>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp894.000</t>
+          <t>Rp1.241.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp8.460.000</t>
+          <t>Rp8.560.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>68</v>
       </c>
       <c r="D63" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp3.110.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>108</v>
       </c>
       <c r="D71" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp4.887.500</t>
+          <t>Rp4.387.500</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.655.000</t>
+          <t>Rp4.165.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>138</v>
       </c>
       <c r="D89" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp4.025.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp3.710.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp318.000</t>
+          <t>Rp442.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5710,16 +5710,16 @@
         <v>90</v>
       </c>
       <c r="D71" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.782.000</t>
+          <t>Rp4.432.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.530.000</t>
+          <t>Rp10.730.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp14.595.000</t>
+          <t>Rp14.870.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.900.000</t>
+          <t>Rp22.300.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.100.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>84</v>
       </c>
       <c r="D35" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.690.000</t>
+          <t>Rp4.088.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.220.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.075.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.739.000</t>
+          <t>Rp5.089.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp28.070.000</t>
+          <t>Rp27.110.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp2.079.000</t>
+          <t>Rp2.178.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-07.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-07.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>69</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.615.986</t>
+          <t>Rp6.319.986</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.975.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.598.000</t>
+          <t>Rp4.797.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.095.000</t>
+          <t>Rp1.245.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>90</v>
       </c>
       <c r="D81" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp2.679.000</t>
+          <t>Rp2.778.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>36</v>
       </c>
       <c r="D92" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp465.000</t>
+          <t>Rp350.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.328.500</t>
+          <t>Rp15.810.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.025.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>36</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp375.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D58" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.240.000</t>
+          <t>Rp1.480.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.150.000</t>
+          <t>Rp7.650.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.875.000</t>
+          <t>Rp6.050.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.730.000</t>
+          <t>Rp11.430.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp804.000</t>
+          <t>Rp942.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.300.000</t>
+          <t>Rp21.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.055.000</t>
+          <t>Rp3.180.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp12.150.000</t>
+          <t>Rp12.250.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>84</v>
       </c>
       <c r="D35" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.088.000</t>
+          <t>Rp4.287.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.220.000</t>
+          <t>Rp2.520.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.125.000</t>
+          <t>Rp7.425.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.399.993</t>
+          <t>Rp3.524.993</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D36" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.520.000</t>
+          <t>Rp1.970.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
